--- a/originales/respuestas/2025/01. Calificadas/bucle p35/Terminal De Transportes.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p35/Terminal De Transportes.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="v8roZ6NV0Ii3AcmgC0InU+BkvWUVNLyAYaGR9ii9iko="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Sb5GFLN/lny/36fda0fkFckTD/F206o0BZum1O/XWU="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>Entidad</t>
   </si>
@@ -72,7 +72,7 @@
     <t>Implementar al 100% el Plan de Gestión del Conocimiento de la TTSA</t>
   </si>
   <si>
-    <t>En el marco del Plan Estratégico de la empresa se tiene como meta Implementar al 100% el Plan de Gestión del Conocimiento de la TTSA, de esta manera, para los años 2024 se formuló como plan de acción:</t>
+    <t>En el marco del Plan Estratégico de la empresa se tiene como meta Implementar al 100% el Plan de Gestión del Conocimiento de la TTSA, de esta manera, para los años 2024 se formuló como plan de acción: Realizar el diagnóstico y definir el Plan de Gestión del Conocimiento e Implementar dos (2) buenas prácticas en materia de Gestión del Conocimiento de la TTSA.</t>
   </si>
   <si>
     <t>https://innovebogota.veeduriadistrital.gov.co:4282/app/api_preguntas/public/api/download-file-by-nombre/208/META GESTIÓN DEL CONOCIMIENTO.pdf</t>
@@ -91,12 +91,6 @@
   </si>
   <si>
     <t>Soporte documental</t>
-  </si>
-  <si>
-    <t>En el marco del Plan Estratégico de la empresa se tiene como meta Implementar al 100% el Plan de Gestión del Conocimiento de la TTSA, de esta manera, para los años 2024 se formuló como plan de acción: Realizar el diagnóstico y definir el Plan de Gestión del Conocimiento y</t>
-  </si>
-  <si>
-    <t>En el marco del Plan Estratégico de la empresa se tiene como meta Implementar al 100% el Plan de Gestión del Conocimiento de la TTSA, de esta manera, para los años 2024 se formuló como plan de acción: Realizar el diagnóstico y definir el Plan de Gestión del Conocimiento e Implementar dos (2) buenas prácticas en materia de Gestión del Conocimiento de la TTSA.</t>
   </si>
 </sst>
 </file>
@@ -535,90 +529,8 @@
       </c>
       <c r="P2" s="4"/>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="O3" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="P3" s="4"/>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M4" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="O4" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="P4" s="4"/>
-    </row>
+    <row r="3" ht="14.25" customHeight="1"/>
+    <row r="4" ht="14.25" customHeight="1"/>
     <row r="5" ht="14.25" customHeight="1"/>
     <row r="6" ht="14.25" customHeight="1"/>
     <row r="7" ht="14.25" customHeight="1"/>
@@ -1613,8 +1525,6 @@
     <row r="996" ht="14.25" customHeight="1"/>
     <row r="997" ht="14.25" customHeight="1"/>
     <row r="998" ht="14.25" customHeight="1"/>
-    <row r="999" ht="14.25" customHeight="1"/>
-    <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
